--- a/human_resources_forms/007_policy_violation_incident_form--human_resources_forms.xlsx
+++ b/human_resources_forms/007_policy_violation_incident_form--human_resources_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -441,9 +441,9 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="39" customWidth="1" min="2" max="2"/>
-    <col width="39" customWidth="1" min="3" max="3"/>
-    <col width="6" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="50" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -548,7 +548,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>incident_description</t>
+          <t>Incident Description</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -561,17 +561,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>employee_name</t>
+          <t>incident_status</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>employee_name</t>
+          <t>Incident Status</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -589,12 +589,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>policy_violation</t>
+          <t>reporting_officer_name</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>policy_violation</t>
+          <t>Reporting Officer</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -612,12 +612,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>policy_violation_details</t>
+          <t>reporting_officer_details</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>policy_violation_details</t>
+          <t>Reporting Officer Details</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -635,12 +635,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>incident_reporting_officer</t>
+          <t>reporting_officer_email</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>incident_reporting_officer</t>
+          <t>Reporting Officer Email</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -653,17 +653,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>incident_status</t>
+          <t>reporting_officer_phone</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>incident_status</t>
+          <t>Reporting Officer Phone</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -676,17 +676,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>incident_status_date</t>
+          <t>reporting_officer_address</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>incident_status_date</t>
+          <t>Reporting Officer Address</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -699,17 +699,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>incident_status_time</t>
+          <t>reporting_officer_department</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>incident_status_time</t>
+          <t>Reporting Officer Department</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -727,12 +727,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>incident_status_reason</t>
+          <t>reporting_officer_job_title</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>incident_status_reason</t>
+          <t>Reporting Officer Job Title</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -750,12 +750,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>incident_reporting_reason</t>
+          <t>reporting_officer_id</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>incident_reporting_reason</t>
+          <t>Reporting Officer ID</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -773,12 +773,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>incident_reporting_officer</t>
+          <t>reporting_officer_notes</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>incident_reporting_officer</t>
+          <t>Reporting Officer Notes</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -796,12 +796,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>incident_reporting_date</t>
+          <t>reporting_officer_date</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>incident_reporting_date</t>
+          <t>Reporting Officer Date</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -819,12 +819,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>incident_reporting_time</t>
+          <t>reporting_officer_time</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>incident_reporting_time</t>
+          <t>Reporting Officer Time</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -847,7 +847,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>incident_reporting_reason</t>
+          <t>Incident Reporting Reason</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -860,17 +860,17 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>incident_reporting_reasons</t>
+          <t>reporting_officer_reason</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>incident_reporting_reasons</t>
+          <t>Reporting Officer Reason</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -883,20 +883,24 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>incident_reporting_officer_notes</t>
+          <t>reporting_officer_reasons</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>incident_reporting_officer_notes</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
+          <t>Select multiple from - Policy Violation, Incident Report, Other</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Select multiple from - Policy Violation, Incident Report, Other</t>
+        </is>
+      </c>
       <c r="E20" t="inlineStr">
         <is>
           <t>no</t>
@@ -911,12 +915,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>incident_reporting_officer_email</t>
+          <t>incident_reporting_officer_notes</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>incident_reporting_officer_email</t>
+          <t>Incident Reporting Officer Notes</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -934,12 +938,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>incident_reporting_officer_phone</t>
+          <t>reporting_officer_email_2</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>incident_reporting_officer_phone</t>
+          <t>Reporting Officer Email 2</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -957,12 +961,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>incident_reporting_officer_address</t>
+          <t>reporting_officer_phone_2</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>incident_reporting_officer_address</t>
+          <t>Reporting Officer Phone 2</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -980,12 +984,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>incident_reporting_officer_department</t>
+          <t>reporting_officer_address_2</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>incident_reporting_officer_department</t>
+          <t>Reporting Officer Address 2</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -1003,12 +1007,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>incident_reporting_officer_job_title</t>
+          <t>reporting_officer_department_2</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>incident_reporting_officer_job_title</t>
+          <t>Reporting Officer Department 2</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1026,12 +1030,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>incident_reporting_officer_id</t>
+          <t>reporting_officer_job_title_2</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>incident_reporting_officer_id</t>
+          <t>Reporting Officer Job Title 2</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1049,12 +1053,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>incident_reporting_officer_notes</t>
+          <t>reporting_officer_id_2</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>incident_reporting_officer_notes</t>
+          <t>Reporting Officer Id 2</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -1067,17 +1071,17 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>incident_reporting_officer_date</t>
+          <t>reporting_officer_notes_2</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>incident_reporting_officer_date</t>
+          <t>Reporting Officer Notes 2</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
@@ -1090,17 +1094,17 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>incident_reporting_officer_time</t>
+          <t>reporting_officer_id_3</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>incident_reporting_officer_time</t>
+          <t>Reporting Officer Id 3</t>
         </is>
       </c>
       <c r="D29" t="inlineStr"/>
@@ -1124,7 +1128,7 @@
   <dimension ref="A1:C7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="36" customWidth="1" min="1" max="1"/>
+    <col width="35" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
   </cols>
@@ -1200,7 +1204,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>incident_reporting_reasons_choices</t>
+          <t>reporting_officer_reasons_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1217,7 +1221,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>incident_reporting_reasons_choices</t>
+          <t>reporting_officer_reasons_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1234,7 +1238,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>incident_reporting_reasons_choices</t>
+          <t>reporting_officer_reasons_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
